--- a/output/pdf_financials_xlsx/TVA.B.xlsx
+++ b/output/pdf_financials_xlsx/TVA.B.xlsx
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>67.51000000000001</v>
+        <v>2.664</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>66.27</v>
+        <v>4.754</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>56.35</v>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">

--- a/output/pdf_financials_xlsx/TVA.B.xlsx
+++ b/output/pdf_financials_xlsx/TVA.B.xlsx
@@ -2763,46 +2763,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.262</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.924</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.605</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.756</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>10.619</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.717</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>11.996</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>17.219</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>21.258</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>18.112</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.383</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.838</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.181</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>13.278</v>
       </c>
     </row>
     <row r="35">
@@ -2885,46 +2885,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.262</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.924</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.605</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.756</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>10.619</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.717</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>11.996</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>17.219</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>21.258</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>18.112</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.383</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.838</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.181</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>13.278</v>
       </c>
     </row>
     <row r="37">
@@ -3617,46 +3617,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.664</v>
+        <v>62.248</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.754</v>
+        <v>64.346</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>56.35</v>
+        <v>50.745</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>74.77</v>
+        <v>73.014</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>83.776</v>
+        <v>73.157</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>71.649</v>
+        <v>63.932</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>83.755</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>102.342</v>
+        <v>90.346</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>102.683</v>
+        <v>85.464</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>105.027</v>
+        <v>83.76900000000001</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>104.001</v>
+        <v>85.889</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>97.41800000000001</v>
+        <v>94.035</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>120.428</v>
+        <v>117.59</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>123.332</v>
+        <v>118.151</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>147.96</v>
@@ -3668,7 +3668,7 @@
         <v>114.47</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>137.443</v>
+        <v>124.165</v>
       </c>
     </row>
     <row r="49">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32868,7 +32868,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">
@@ -33188,7 +33188,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">

--- a/output/pdf_financials_xlsx/TVA.B.xlsx
+++ b/output/pdf_financials_xlsx/TVA.B.xlsx
@@ -36272,7 +36272,11 @@
           <t>Additions to intangible assets 12</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -39788,7 +39792,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -41524,7 +41532,11 @@
           <t>Additions to intangible assets 15</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -42646,7 +42658,11 @@
           <t>Additions to intangible assets 14</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -45994,7 +46010,11 @@
           <t>Additions to intangible assets 16</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -51162,7 +51182,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E410" s="5" t="n">
         <v>-4.768</v>
       </c>

--- a/output/pdf_financials_xlsx/TVA.B.xlsx
+++ b/output/pdf_financials_xlsx/TVA.B.xlsx
@@ -720,10 +720,8 @@
       <c r="R5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -882,10 +880,8 @@
       <c r="R7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -947,10 +943,8 @@
       <c r="R8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1012,10 +1006,8 @@
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1077,10 +1069,8 @@
       <c r="R10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1239,10 +1229,8 @@
       <c r="R12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1304,10 +1292,8 @@
       <c r="R13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1369,10 +1355,8 @@
       <c r="R14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1434,10 +1418,8 @@
       <c r="R15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1491,18 +1473,16 @@
         <v>17.027</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-17.179</v>
+        <v>-12.002</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-48.563</v>
+        <v>-63.606</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-19.343</v>
-      </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-23.042</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>19.831</v>
       </c>
     </row>
     <row r="17">
@@ -1556,18 +1536,16 @@
         <v>13.467</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>3.113</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.672</v>
+        <v>15.715</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="S17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.699</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>-5.044</v>
       </c>
     </row>
     <row r="18">
@@ -1823,10 +1801,8 @@
       <c r="R20" s="3" t="n">
         <v>-19.343</v>
       </c>
-      <c r="S20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S20" s="3" t="n">
+        <v>14.787</v>
       </c>
     </row>
     <row r="21">
@@ -1888,10 +1864,8 @@
       <c r="R21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1953,10 +1927,8 @@
       <c r="R22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2018,10 +1990,8 @@
       <c r="R23" s="3" t="n">
         <v>-19.343</v>
       </c>
-      <c r="S23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S23" s="3" t="n">
+        <v>14.787</v>
       </c>
     </row>
     <row r="24">
@@ -2348,18 +2318,16 @@
         <v>17.027</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-17.179</v>
+        <v>-12.002</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-48.563</v>
+        <v>-63.606</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-19.343</v>
-      </c>
-      <c r="S27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-23.042</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>19.831</v>
       </c>
     </row>
     <row r="28">
@@ -2476,18 +2444,16 @@
         <v>17.027</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-17.179</v>
+        <v>-12.002</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-48.563</v>
+        <v>-63.606</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-19.343</v>
-      </c>
-      <c r="S29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-23.042</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>19.831</v>
       </c>
     </row>
     <row r="30">
@@ -2638,18 +2604,16 @@
         <v>79.09203030481001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-48.25659235112638</v>
+        <v>-25.93734377603732</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-1.383769536478389</v>
+        <v>-24.70678866773575</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.05329398489715</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>25.43492511724069</v>
       </c>
     </row>
     <row r="32">
@@ -3147,40 +3111,40 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>19.991</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>19.751</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>22.533</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>21.345</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>21.487</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>28.654</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>24.539</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>28.99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>32.689</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>25.442</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>22.823</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>19.327</v>
       </c>
     </row>
     <row r="41">
@@ -3208,40 +3172,40 @@
         <v>136.408</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>136.811</v>
+        <v>156.802</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>150.93</v>
+        <v>170.681</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>142.663</v>
+        <v>165.196</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>144.913</v>
+        <v>166.258</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>151.715</v>
+        <v>173.202</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>160.552</v>
+        <v>189.206</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>154.06</v>
+        <v>178.599</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>210.814</v>
+        <v>239.804</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>175.174</v>
+        <v>207.863</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>154.065</v>
+        <v>179.507</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>134.835</v>
+        <v>157.658</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>154.453</v>
+        <v>173.78</v>
       </c>
     </row>
     <row r="42">
@@ -3635,40 +3599,40 @@
         <v>63.932</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>83.755</v>
+        <v>63.764</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>90.346</v>
+        <v>70.595</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>85.464</v>
+        <v>62.931</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>83.76900000000001</v>
+        <v>62.424</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>85.889</v>
+        <v>64.402</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>94.035</v>
+        <v>65.381</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>117.59</v>
+        <v>93.051</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>118.151</v>
+        <v>89.161</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>147.96</v>
+        <v>115.271</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>156.842</v>
+        <v>131.4</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>114.47</v>
+        <v>91.64700000000001</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>124.165</v>
+        <v>104.838</v>
       </c>
     </row>
     <row r="49">
@@ -4637,10 +4601,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>87.209</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>71.486</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -6782,10 +6746,8 @@
       <c r="R99" s="3" t="n">
         <v>-19.343</v>
       </c>
-      <c r="S99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S99" s="3" t="n">
+        <v>14.787</v>
       </c>
     </row>
     <row r="100">
@@ -8216,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>74.73699999999999</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>0</v>
@@ -8338,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-75</v>
+        <v>-0.263</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>-0.9399999999999999</v>
@@ -35206,7 +35168,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -44960,7 +44926,11 @@
           <t>Increase of long-term debt 19</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -50764,7 +50734,11 @@
           <t>Future income taxes (note 4)</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -53296,7 +53270,11 @@
           <t>Future income taxes (note 5)</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E430" s="5" t="n">
         <v>-3.18</v>
       </c>
@@ -56366,7 +56344,11 @@
           <t>Income taxes (income tax recovery) 6</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -57084,7 +57066,11 @@
           <t>Income tax recovery 6</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
